--- a/mapping/mapping_file_wl.xlsx
+++ b/mapping/mapping_file_wl.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SOLIZA\Documents\secret\mapping\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\Desktop\eod_report\mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0235AC73-D444-44A7-8D2B-3EFF46FCEB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8528C-0400-4EF0-B9E3-6E604AD3EEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{64C44B07-5FB7-43A0-AC1F-68027E67D306}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{64C44B07-5FB7-43A0-AC1F-68027E67D306}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -153,7 +153,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,13 +163,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -183,13 +176,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -221,18 +214,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,118 +562,119 @@
   <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -762,9 +753,10 @@
       <c r="Z2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="4"/>
+      <c r="AA2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="65" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mapping/mapping_file_wl.xlsx
+++ b/mapping/mapping_file_wl.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SPM\Desktop\eod_report\mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8528C-0400-4EF0-B9E3-6E604AD3EEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00537527-B904-47B0-A422-1E2324D630DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{64C44B07-5FB7-43A0-AC1F-68027E67D306}"/>
+    <workbookView xWindow="12390" yWindow="4995" windowWidth="11520" windowHeight="7785" xr2:uid="{64C44B07-5FB7-43A0-AC1F-68027E67D306}"/>
   </bookViews>
   <sheets>
     <sheet name="mapping" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="85">
   <si>
     <t>CUST_ID</t>
   </si>
@@ -125,9 +123,6 @@
     <t>LPA</t>
   </si>
   <si>
-    <t>Aging</t>
-  </si>
-  <si>
     <t>HO_FLAG</t>
   </si>
   <si>
@@ -146,14 +141,165 @@
     <t>BLOCK_CODE</t>
   </si>
   <si>
-    <t>BALANCE TYPE</t>
+    <t>TPAP</t>
+  </si>
+  <si>
+    <t>OTHER CONTACT</t>
+  </si>
+  <si>
+    <t>ADDRESS</t>
+  </si>
+  <si>
+    <t>GENDER</t>
+  </si>
+  <si>
+    <t>TCL</t>
+  </si>
+  <si>
+    <t>DELINQUENCY_STRING</t>
+  </si>
+  <si>
+    <t>ADA_ACCOUNT</t>
+  </si>
+  <si>
+    <t>DEBIT_AMOUNT_PREFERENCE</t>
+  </si>
+  <si>
+    <t>BIRTHDATE</t>
+  </si>
+  <si>
+    <t>UNIBANKER</t>
+  </si>
+  <si>
+    <t>MEMO_LINE</t>
+  </si>
+  <si>
+    <t>AREA CODE</t>
+  </si>
+  <si>
+    <t>CATEGORY/CLASSIF</t>
+  </si>
+  <si>
+    <t>Balance Type</t>
+  </si>
+  <si>
+    <t>CONTACTED BY</t>
+  </si>
+  <si>
+    <t>TPAP DD</t>
+  </si>
+  <si>
+    <t>CLASSIF 2</t>
+  </si>
+  <si>
+    <t>EMAIL NOTI</t>
+  </si>
+  <si>
+    <t>CATEGORY</t>
+  </si>
+  <si>
+    <t>CREDIT_LIMIT</t>
+  </si>
+  <si>
+    <t>AMOUNT_OUTSTANDING</t>
+  </si>
+  <si>
+    <t>AMOUNT_OVERDUE</t>
+  </si>
+  <si>
+    <t>MIN_AMOUNT_DUE</t>
+  </si>
+  <si>
+    <t>XDAYS</t>
+  </si>
+  <si>
+    <t>LAST_PAYMENT_AMT</t>
+  </si>
+  <si>
+    <t>OTHER_CONTACT</t>
+  </si>
+  <si>
+    <t>CUST ID</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Other contact</t>
+  </si>
+  <si>
+    <t>TU RESULT</t>
+  </si>
+  <si>
+    <t>BOS/CB</t>
+  </si>
+  <si>
+    <t>Last Payment Date</t>
+  </si>
+  <si>
+    <t>ADA ACCT</t>
+  </si>
+  <si>
+    <t>DAP</t>
+  </si>
+  <si>
+    <t>Unit Code</t>
+  </si>
+  <si>
+    <t>TPAP CLASSIF</t>
+  </si>
+  <si>
+    <t>BLOCK CODE</t>
+  </si>
+  <si>
+    <t>D CUST OPEN</t>
+  </si>
+  <si>
+    <t>ZIP CODE</t>
+  </si>
+  <si>
+    <t>LAST DUE DATE (manual)</t>
+  </si>
+  <si>
+    <t>BLANCE TYPE</t>
+  </si>
+  <si>
+    <t>PTP AMT</t>
+  </si>
+  <si>
+    <t>Amount_Overdue</t>
+  </si>
+  <si>
+    <t>XDAYS_AMOUNT</t>
+  </si>
+  <si>
+    <t>LAST PAYMENT DATE</t>
+  </si>
+  <si>
+    <t>Loan Number</t>
+  </si>
+  <si>
+    <t>Amount Overdue</t>
+  </si>
+  <si>
+    <t>UnitCode</t>
+  </si>
+  <si>
+    <t>AREA_CODE</t>
+  </si>
+  <si>
+    <t>Balance Type (100k up, etc)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="0000000000000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ "/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,7 +309,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -176,18 +338,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -195,42 +357,295 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{3D12A0A2-AC90-45EB-ABF2-754CC88C2F59}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{C573BA4E-B6AA-4833-B450-3B3041C1ECCC}"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{EF4B6E8F-B032-4289-86F0-7B9ADDE25C6B}">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{59911D48-B23A-4999-BFAB-7B44063A4AE5}">
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -559,201 +974,638 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75D7E53C-5C71-4B9F-9B2E-3BCBAF3D6F26}">
-  <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AS6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="33.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="25.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:45" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="R1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="S1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="X1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Y1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="Z1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="AA1" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="AD1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="AG1" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="AI1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="AM1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS1" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA2" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AK2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AO2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AQ2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>14</v>
+      <c r="AR2" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AS2" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="3" spans="1:45" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" s="2"/>
+      <c r="T3" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="U3" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V3" s="2"/>
+      <c r="W3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="11"/>
+      <c r="AB3" s="11"/>
+      <c r="AC3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD3" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK3" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL3" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM3" s="2"/>
+      <c r="AN3" s="2"/>
+      <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
+      <c r="AQ3" s="2"/>
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="2"/>
+    </row>
+    <row r="4" spans="1:45" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="S4" s="2"/>
+      <c r="T4" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="11"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG4" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AL4" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM4" s="2"/>
+      <c r="AN4" s="2"/>
+      <c r="AO4" s="2"/>
+      <c r="AP4" s="2"/>
+      <c r="AQ4" s="2"/>
+      <c r="AR4" s="2"/>
+      <c r="AS4" s="2"/>
+    </row>
+    <row r="5" spans="1:45" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" s="3" t="s">
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL5" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2"/>
+      <c r="AP5" s="2"/>
+      <c r="AQ5" s="2"/>
+      <c r="AR5" s="2"/>
+      <c r="AS5" s="2"/>
+    </row>
+    <row r="6" spans="1:45" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="AK6" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="X2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="1"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+      <c r="AN6" s="2"/>
+      <c r="AO6" s="2"/>
+      <c r="AP6" s="2"/>
+      <c r="AQ6" s="2"/>
+      <c r="AR6" s="2"/>
+      <c r="AS6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
